--- a/audio/Memorial Hall/mic_inventory.xlsx
+++ b/audio/Memorial Hall/mic_inventory.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mic Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mic Inventory" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1143,96 +1143,96 @@
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Shure PG52</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Cardioid</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Bass cabinet (best use); floor tom; kick when the Beta 52/D6 are committed</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>No phantom</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Discontinued (superseded by PGA52). 30Hz-13kHz, 300 ohm, -55 dBV/Pa, 470g. Curve humps 60-100Hz, dips 200-800Hz, rises 4-5kHz. Never boost the hump; never cut into the dip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SMALL DIAPHRAGM CONDENSERS</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Primary Applications</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>48V Phantom</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Kit / Source</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Lauten Snare Mic</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Cardioid</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Snare drum — purpose-built FET condenser; studio, live, and touring</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>LS-408; 28dB off-axis rejection; onboard HP (flat/80Hz/140Hz) &amp; LP (flat/12kHz/5kHz) filters; articulating swivel mount included</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Schoeps CMC6 + MK4</t>
+          <t>Lauten Snare Mic</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Classical overheads, acoustic soloists, spot mics</t>
+          <t>Snare drum — purpose-built FET condenser; studio, live, and touring</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Interchangeable cap body</t>
+          <t>LS-408; 28dB off-axis rejection; onboard HP (flat/80Hz/140Hz) &amp; LP (flat/12kHz/5kHz) filters; articulating swivel mount included</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Schoeps CMC6 + MK5</t>
+          <t>Schoeps CMC6 + MK4</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Omni / Cardioid</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Classical room, Decca tree, wide ambient</t>
+          <t>Classical overheads, acoustic soloists, spot mics</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Switchable omni or cardioid</t>
+          <t>Interchangeable cap body</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Sennheiser MKH 40</t>
+          <t>Schoeps CMC6 + MK5</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Omni / Cardioid</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Classical main pair — ORTF, NOS, spaced omni</t>
+          <t>Classical room, Decca tree, wide ambient</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Pair; extremely low self-noise. First-call classical main.</t>
+          <t>Switchable omni or cardioid</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>DPA 4099</t>
+          <t>Sennheiser MKH 40</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Supercardioid</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Instrument clip — strings, brass, woodwinds, piano, guitar; spot mic on kit</t>
+          <t>Classical main pair — ORTF, NOS, spaced omni</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1373,14 +1373,14 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>144 dB SPL; instrument-specific mounts</t>
+          <t>Pair; extremely low self-noise. First-call classical main.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Shure SM81</t>
+          <t>DPA 4099</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Supercardioid</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Overheads, hi-hat, acoustic instruments</t>
+          <t>Instrument clip — strings, brass, woodwinds, piano, guitar; spot mic on kit</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1408,12 +1408,16 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>144 dB SPL; instrument-specific mounts</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Shure Beta 91</t>
+          <t>Shure SM81</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1423,12 +1427,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Boundary (half-card.)</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Kick drum — attack layer (inside, on head)</t>
+          <t>Overheads, hi-hat, acoustic instruments</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1441,16 +1445,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Pair with Beta 52</t>
-        </is>
-      </c>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>AKG C422</t>
+          <t>Shure Beta 91</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Stereo coincident</t>
+          <t>Boundary (half-card.)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Stereo overheads, acoustic piano</t>
+          <t>Kick drum — attack layer (inside, on head)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1480,14 +1480,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>XY stereo pair in one body</t>
+          <t>Pair with Beta 52</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Audix M1280BHC</t>
+          <t>AKG C422</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Stereo coincident</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Hi-hat — ultra-compact condenser clip mic</t>
+          <t>Stereo overheads, acoustic piano</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1512,15 +1512,19 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Audix DP8</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>XY stereo pair in one body</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Audix M1280B</t>
+          <t>Audix M1280BHC</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1535,7 +1539,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Overheads / cymbals — compact matched pair</t>
+          <t>Hi-hat — ultra-compact condenser clip mic</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1548,16 +1552,12 @@
           <t>Audix DP8</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>×2 in DP8</t>
-        </is>
-      </c>
+      <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Earthworks DM6</t>
+          <t>Audix M1280B</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Supercardioid</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Kick drum — condenser; wide freq response; solo or layer with dynamic</t>
+          <t>Overheads / cymbals — compact matched pair</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1582,19 +1582,19 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Earthworks DK-6</t>
+          <t>Audix DP8</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Triad-Orbit M2-R mount included</t>
+          <t>×2 in DP8</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Earthworks DM17</t>
+          <t>Earthworks DM6</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Supercardioid</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Snare, toms — rim-mount (RM3); condenser clarity on kit</t>
+          <t>Kick drum — condenser; wide freq response; solo or layer with dynamic</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1624,14 +1624,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>×4 in kit; RM3 rim mounts included</t>
+          <t>Triad-Orbit M2-R mount included</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Earthworks SR20sp G2</t>
+          <t>Earthworks DM17</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Drum overheads — matched stereo pair</t>
+          <t>Snare, toms — rim-mount (RM3); condenser clarity on kit</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1659,12 +1659,16 @@
           <t>Earthworks DK-6</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>×4 in kit; RM3 rim mounts included</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Earthworks SR25</t>
+          <t>Earthworks SR20sp G2</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -1679,7 +1683,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Overheads (×2) or kick (×1) — 3 mics in DK-25</t>
+          <t>Drum overheads — matched stereo pair</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1689,19 +1693,15 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Earthworks DK-25</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>×3 in kit</t>
-        </is>
-      </c>
+          <t>Earthworks DK-6</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>sE sE8</t>
+          <t>Earthworks SR25</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Drum overheads — matched stereo pair</t>
+          <t>Overheads (×2) or kick (×1) — 3 mics in DK-25</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1726,15 +1726,19 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>sE V Pack Arena</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
+          <t>Earthworks DK-25</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>×3 in kit</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Line Audio OM1</t>
+          <t>sE sE8</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1744,12 +1748,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Omni pressure</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Crowd / ambient — flown 18' above stage at The Memo</t>
+          <t>Drum overheads — matched stereo pair</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1759,19 +1763,15 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Pair; EQ starting points in venue-notes.md</t>
-        </is>
-      </c>
+          <t>sE V Pack Arena</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Line Audio CM4</t>
+          <t>Line Audio OM1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Cardioid (ORTF pr)</t>
+          <t>Omni pressure</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Crowd, balcony rear-facing at The Memo</t>
+          <t>Crowd / ambient — flown 18' above stage at The Memo</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1808,131 +1808,131 @@
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Line Audio CM4</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Cardioid (ORTF pr)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Crowd, balcony rear-facing at The Memo</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Pair; EQ starting points in venue-notes.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>Deity S2</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>SDC / Shotgun</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Short shotgun</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Crowd — under main-floor PA, aimed into audience at The Memo</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Pair; EQ starting points in venue-notes.md</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>LARGE DIAPHRAGM CONDENSERS</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Primary Applications</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>48V Phantom</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Kit / Source</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Neumann KMS 105</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>LDC</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Supercardioid</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Lead vocals (stage condenser) — detail and presence over dynamics</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Designed for live handheld use</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Neumann TLM 102</t>
+          <t>Neumann KMS 105</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Supercardioid</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Studio/recording vocals, acoustic instruments, overheads</t>
+          <t>Lead vocals (stage condenser) — detail and presence over dynamics</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1962,14 +1962,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Transformerless; low self-noise</t>
+          <t>Designed for live handheld use</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>AKG C414</t>
+          <t>Neumann TLM 102</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Omni/Card/Fig-8/Supercard</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Versatile — room, overheads, vocals, brass, strings</t>
+          <t>Studio/recording vocals, acoustic instruments, overheads</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Multiple pattern/pad/HPF switches</t>
+          <t>Transformerless; low self-noise</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Shure Beta 27</t>
+          <t>AKG C414</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Cardioid</t>
+          <t>Omni/Card/Fig-8/Supercard</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Vocals, overheads, acoustic instruments</t>
+          <t>Versatile — room, overheads, vocals, brass, strings</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Low-cut &amp; −15 dB pad switches</t>
+          <t>Multiple pattern/pad/HPF switches</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Warm Audio WA-87</t>
+          <t>Shure Beta 27</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Omni / Cardioid / Fig-8</t>
+          <t>Cardioid</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Vocals, room, overheads, acoustic instruments</t>
+          <t>Vocals, overheads, acoustic instruments</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2073,138 +2073,138 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Transformer-coupled; U87-inspired; multi-pattern; low-cut &amp; pad switches</t>
+          <t>Low-cut &amp; −15 dB pad switches</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>Warm Audio WA-87</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>LDC</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Omni / Cardioid / Fig-8</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Vocals, room, overheads, acoustic instruments</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Transformer-coupled; U87-inspired; multi-pattern; low-cut &amp; pad switches</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>Warm Audio WA-14</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>LDC</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Omni / Cardioid / Fig-8</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Vocals, room, overheads, instruments — versatile multi-pattern</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Transformer-coupled; C414-inspired; multiple pattern/pad/HPF switches</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>RIBBONS</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="11" t="n"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Primary Applications</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>48V Phantom</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Kit / Source</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Royer R-121</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Ribbon</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Figure-8</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Guitar cab blend mic (pair with SM57)</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>⚠ NO 48V — destroys ribbon</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>Sit 6–10 dB below SM57; polarity-check in mono; VCA-group with SM57 (CH 13/15 at Memo)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Royer R-10</t>
+          <t>Royer R-121</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Guitar cab, room, acoustic instruments — alt to R-121</t>
+          <t>Guitar cab blend mic (pair with SM57)</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2232,136 +2232,136 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Sit 6–10 dB below SM57; polarity-check in mono; VCA-group with SM57 (CH 13/15 at Memo)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
+          <t>Royer R-10</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Ribbon</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Figure-8</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Guitar cab, room, acoustic instruments — alt to R-121</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>⚠ NO 48V — destroys ribbon</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
           <t>AEA R88</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Ribbon</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Stereo Fig-8 (Blumlein)</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Room, overhead, acoustic ensemble</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>⚠ NO 48V — destroys ribbon</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>High output — watch gain; handle with care</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>DIs — DIRECT BOXES</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="11" t="n"/>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Primary Applications</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>48V Phantom</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Kit / Source</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Radial J48</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Active (phantom)</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>General-purpose DI — keys, bass, acoustic guitar, playback</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Jensen-style transformer output</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Radial ProDI</t>
+          <t>Radial J48</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Active (phantom)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>General-purpose passive DI — guitar, bass, keys, acoustic</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>No phantom</t>
+          <t>General-purpose DI — keys, bass, acoustic guitar, playback</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2391,42 +2391,79 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Passive; transformer-isolated; no power required</t>
+          <t>Jensen-style transformer output</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>Radial ProDI</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>General-purpose passive DI — guitar, bass, keys, acoustic</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>No phantom</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Passive; transformer-isolated; no power required</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>Neve RNDI</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Active (phantom)</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Hi-Z instrument — electric bass, guitar direct, synth</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Requires 48V</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Standalone</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Requires 48V</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Standalone</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>Transformer-balanced; excellent for bass clarity</t>
         </is>
